--- a/coastal-air-plus-ytd-oct23-campaigns.xlsx
+++ b/coastal-air-plus-ytd-oct23-campaigns.xlsx
@@ -13,7 +13,7 @@
     <sheet name="By Channel" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Campaigns Ranked'!$A$4:$J$60</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Campaigns Ranked'!$A$4:$L$60</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +30,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B9" authorId="0">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="83">
   <si>
     <t xml:space="preserve">Coastal Air Plus — YTD Totals (Jan 1 – Oct 23, 2026)</t>
   </si>
@@ -83,12 +83,21 @@
     <t xml:space="preserve">Unique Leads</t>
   </si>
   <si>
+    <t xml:space="preserve">Booked Jobs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Closed Revenue (tracked)</t>
   </si>
   <si>
     <t xml:space="preserve">Cost per Unique Lead</t>
   </si>
   <si>
+    <t xml:space="preserve">Cost per Booked Job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book Rate</t>
+  </si>
+  <si>
     <t xml:space="preserve">ROAS (Closed)</t>
   </si>
   <si>
@@ -104,12 +113,12 @@
     <t xml:space="preserve">All figures except brand-assisted come from Searchlight's performance-by export for Jan 1 – Oct 23, 2026, as one period.</t>
   </si>
   <si>
+    <t xml:space="preserve">Booked jobs = Searchlight "Booked Customers". Book rate = booked jobs ÷ unique leads.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unique leads are counted per campaign on the campaign sheet; the channel total matches Searchlight's report.</t>
   </si>
   <si>
-    <t xml:space="preserve">Booked jobs are not included in this export.</t>
-  </si>
-  <si>
     <t xml:space="preserve">October revenue is still maturing as recent jobs close.</t>
   </si>
   <si>
@@ -135,9 +144,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cost per Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue per Lead</t>
   </si>
   <si>
     <t xml:space="preserve">Charleston GBP | Search</t>
@@ -318,13 +324,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.00\x;;\-"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="0.00\x;;\-"/>
+    <numFmt numFmtId="170" formatCode="0%;;\-"/>
+    <numFmt numFmtId="171" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -445,7 +453,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -474,6 +482,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -494,6 +506,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -502,7 +518,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -514,15 +534,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -815,7 +839,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -858,69 +882,96 @@
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <f aca="false">'By Channel'!E10</f>
-        <v>841452.23</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <f aca="false">B3/B5</f>
-        <v>48.1238831995572</v>
+      <c r="B7" s="3" t="n">
+        <f aca="false">'By Channel'!F10</f>
+        <v>841452.23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n">
-        <f aca="false">B6/B3</f>
-        <v>4.83950385454001</v>
+      <c r="B8" s="5" t="n">
+        <f aca="false">B3/B5</f>
+        <v>48.1238831995572</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>225000</v>
+      <c r="B9" s="5" t="n">
+        <f aca="false">B3/B6</f>
+        <v>243.517633053221</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="n">
-        <f aca="false">B6+B9</f>
-        <v>1066452.23</v>
+      <c r="B10" s="6" t="n">
+        <f aca="false">B6/B5</f>
+        <v>0.197619706615001</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <f aca="false">B7/B3</f>
+        <v>4.83950385454001</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>225000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
         <v>11</v>
       </c>
+      <c r="B13" s="3" t="n">
+        <f aca="false">B7+B12</f>
+        <v>1066452.23</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -940,2072 +991,2481 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>15</v>
+      <c r="A2" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="B4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>22</v>
+      <c r="G4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11" t="n">
+      <c r="B5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>951</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="H5" s="8" t="n">
         <v>213906.51</v>
       </c>
-      <c r="H5" s="6" t="str">
-        <f aca="false">IF(D5&gt;0,G5/D5,"")</f>
-        <v/>
-      </c>
-      <c r="I5" s="3" t="str">
+      <c r="I5" s="7" t="str">
+        <f aca="false">IF(D5&gt;0,H5/D5,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="3" t="str">
         <f aca="false">IF(AND(D5&gt;0,F5&gt;0),D5/F5,"")</f>
         <v/>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="K5" s="3" t="str">
+        <f aca="false">IF(AND(D5&gt;0,G5&gt;0),D5/G5,"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="13" t="n">
         <f aca="false">IF(F5&gt;0,G5/F5,"")</f>
-        <v>336.330990566038</v>
+        <v>0.0738993710691824</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="B6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>237</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="H6" s="8" t="n">
         <v>90249.74</v>
       </c>
-      <c r="H6" s="6" t="str">
-        <f aca="false">IF(D6&gt;0,G6/D6,"")</f>
-        <v/>
-      </c>
-      <c r="I6" s="3" t="str">
+      <c r="I6" s="7" t="str">
+        <f aca="false">IF(D6&gt;0,H6/D6,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="3" t="str">
         <f aca="false">IF(AND(D6&gt;0,F6&gt;0),D6/F6,"")</f>
         <v/>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="3" t="str">
+        <f aca="false">IF(AND(D6&gt;0,G6&gt;0),D6/G6,"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="13" t="n">
         <f aca="false">IF(F6&gt;0,G6/F6,"")</f>
-        <v>571.200886075949</v>
+        <v>0.278481012658228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="B7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>29624.7</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>450</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>358</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="H7" s="8" t="n">
         <v>75643.91</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <f aca="false">IF(D7&gt;0,G7/D7,"")</f>
+      <c r="I7" s="7" t="n">
+        <f aca="false">IF(D7&gt;0,H7/D7,"")</f>
         <v>2.55340678555395</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <f aca="false">IF(AND(D7&gt;0,F7&gt;0),D7/F7,"")</f>
         <v>82.7505586592179</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="K7" s="3" t="n">
+        <f aca="false">IF(AND(D7&gt;0,G7&gt;0),D7/G7,"")</f>
+        <v>240.851219512195</v>
+      </c>
+      <c r="L7" s="13" t="n">
         <f aca="false">IF(F7&gt;0,G7/F7,"")</f>
-        <v>211.295837988827</v>
+        <v>0.343575418994413</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="7" t="n">
+      <c r="B8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>7574.43</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>302</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>161</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>71450.46</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <f aca="false">IF(D8&gt;0,G8/D8,"")</f>
+      <c r="I8" s="7" t="n">
+        <f aca="false">IF(D8&gt;0,H8/D8,"")</f>
         <v>9.43311377885861</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <f aca="false">IF(AND(D8&gt;0,F8&gt;0),D8/F8,"")</f>
         <v>47.046149068323</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="K8" s="3" t="n">
+        <f aca="false">IF(AND(D8&gt;0,G8&gt;0),D8/G8,"")</f>
+        <v>97.1080769230769</v>
+      </c>
+      <c r="L8" s="13" t="n">
         <f aca="false">IF(F8&gt;0,G8/F8,"")</f>
-        <v>443.791677018634</v>
+        <v>0.484472049689441</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="8" t="n">
         <v>6344.48</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>185</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" s="8" t="n">
         <v>70243.49</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <f aca="false">IF(D9&gt;0,G9/D9,"")</f>
+      <c r="I9" s="7" t="n">
+        <f aca="false">IF(D9&gt;0,H9/D9,"")</f>
         <v>11.0715913676141</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <f aca="false">IF(AND(D9&gt;0,F9&gt;0),D9/F9,"")</f>
         <v>52.8706666666667</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="K9" s="3" t="n">
+        <f aca="false">IF(AND(D9&gt;0,G9&gt;0),D9/G9,"")</f>
+        <v>126.8896</v>
+      </c>
+      <c r="L9" s="13" t="n">
         <f aca="false">IF(F9&gt;0,G9/F9,"")</f>
-        <v>585.362416666667</v>
+        <v>0.416666666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="7" t="n">
+      <c r="B10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="8" t="n">
         <v>26983.14</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>376</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>326</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="H10" s="8" t="n">
         <v>56576.89</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <f aca="false">IF(D10&gt;0,G10/D10,"")</f>
+      <c r="I10" s="7" t="n">
+        <f aca="false">IF(D10&gt;0,H10/D10,"")</f>
         <v>2.09674967405573</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <f aca="false">IF(AND(D10&gt;0,F10&gt;0),D10/F10,"")</f>
         <v>82.7703680981595</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="K10" s="3" t="n">
+        <f aca="false">IF(AND(D10&gt;0,G10&gt;0),D10/G10,"")</f>
+        <v>481.841785714286</v>
+      </c>
+      <c r="L10" s="13" t="n">
         <f aca="false">IF(F10&gt;0,G10/F10,"")</f>
-        <v>173.548742331288</v>
+        <v>0.171779141104294</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11" t="n">
+      <c r="B11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H11" s="8" t="n">
         <v>54290.77</v>
       </c>
-      <c r="H11" s="6" t="str">
-        <f aca="false">IF(D11&gt;0,G11/D11,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="3" t="str">
+      <c r="I11" s="7" t="str">
+        <f aca="false">IF(D11&gt;0,H11/D11,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="3" t="str">
         <f aca="false">IF(AND(D11&gt;0,F11&gt;0),D11/F11,"")</f>
         <v/>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="K11" s="3" t="str">
+        <f aca="false">IF(AND(D11&gt;0,G11&gt;0),D11/G11,"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="13" t="n">
         <f aca="false">IF(F11&gt;0,G11/F11,"")</f>
-        <v>1005.38462962963</v>
+        <v>0.388888888888889</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="B12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H12" s="8" t="n">
         <v>50470.76</v>
       </c>
-      <c r="H12" s="6" t="str">
-        <f aca="false">IF(D12&gt;0,G12/D12,"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="3" t="str">
+      <c r="I12" s="7" t="str">
+        <f aca="false">IF(D12&gt;0,H12/D12,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="3" t="str">
         <f aca="false">IF(AND(D12&gt;0,F12&gt;0),D12/F12,"")</f>
         <v/>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="K12" s="3" t="str">
+        <f aca="false">IF(AND(D12&gt;0,G12&gt;0),D12/G12,"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="13" t="n">
         <f aca="false">IF(F12&gt;0,G12/F12,"")</f>
-        <v>504.7076</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="B13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>302</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>245</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H13" s="8" t="n">
         <v>25849.15</v>
       </c>
-      <c r="H13" s="6" t="str">
-        <f aca="false">IF(D13&gt;0,G13/D13,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="3" t="str">
+      <c r="I13" s="7" t="str">
+        <f aca="false">IF(D13&gt;0,H13/D13,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="3" t="str">
         <f aca="false">IF(AND(D13&gt;0,F13&gt;0),D13/F13,"")</f>
         <v/>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="K13" s="3" t="str">
+        <f aca="false">IF(AND(D13&gt;0,G13&gt;0),D13/G13,"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="13" t="n">
         <f aca="false">IF(F13&gt;0,G13/F13,"")</f>
-        <v>105.506734693878</v>
+        <v>0.126530612244898</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="B14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>18030.7</v>
       </c>
-      <c r="H14" s="6" t="str">
-        <f aca="false">IF(D14&gt;0,G14/D14,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="3" t="str">
+      <c r="I14" s="7" t="str">
+        <f aca="false">IF(D14&gt;0,H14/D14,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="3" t="str">
         <f aca="false">IF(AND(D14&gt;0,F14&gt;0),D14/F14,"")</f>
         <v/>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="K14" s="3" t="str">
+        <f aca="false">IF(AND(D14&gt;0,G14&gt;0),D14/G14,"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="13" t="n">
         <f aca="false">IF(F14&gt;0,G14/F14,"")</f>
-        <v>171.720952380952</v>
+        <v>0.00952380952380953</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="B15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <v>10467.48</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" s="8" t="n">
         <v>16999.08</v>
       </c>
-      <c r="H15" s="6" t="n">
-        <f aca="false">IF(D15&gt;0,G15/D15,"")</f>
+      <c r="I15" s="7" t="n">
+        <f aca="false">IF(D15&gt;0,H15/D15,"")</f>
         <v>1.62398972818673</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="J15" s="3" t="n">
         <f aca="false">IF(AND(D15&gt;0,F15&gt;0),D15/F15,"")</f>
         <v>60.8574418604651</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="K15" s="3" t="n">
+        <f aca="false">IF(AND(D15&gt;0,G15&gt;0),D15/G15,"")</f>
+        <v>261.687</v>
+      </c>
+      <c r="L15" s="13" t="n">
         <f aca="false">IF(F15&gt;0,G15/F15,"")</f>
-        <v>98.8318604651163</v>
+        <v>0.232558139534884</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="11" t="n">
+      <c r="B16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12" t="n">
         <v>192</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>16989.16</v>
       </c>
-      <c r="H16" s="6" t="str">
-        <f aca="false">IF(D16&gt;0,G16/D16,"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="3" t="str">
+      <c r="I16" s="7" t="str">
+        <f aca="false">IF(D16&gt;0,H16/D16,"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="3" t="str">
         <f aca="false">IF(AND(D16&gt;0,F16&gt;0),D16/F16,"")</f>
         <v/>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="K16" s="3" t="str">
+        <f aca="false">IF(AND(D16&gt;0,G16&gt;0),D16/G16,"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="13" t="n">
         <f aca="false">IF(F16&gt;0,G16/F16,"")</f>
-        <v>153.055495495496</v>
+        <v>0.126126126126126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="11" t="n">
+      <c r="B17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
         <v>230</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" s="8" t="n">
         <v>16929.76</v>
       </c>
-      <c r="H17" s="6" t="str">
-        <f aca="false">IF(D17&gt;0,G17/D17,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="3" t="str">
+      <c r="I17" s="7" t="str">
+        <f aca="false">IF(D17&gt;0,H17/D17,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="3" t="str">
         <f aca="false">IF(AND(D17&gt;0,F17&gt;0),D17/F17,"")</f>
         <v/>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="K17" s="3" t="str">
+        <f aca="false">IF(AND(D17&gt;0,G17&gt;0),D17/G17,"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="13" t="n">
         <f aca="false">IF(F17&gt;0,G17/F17,"")</f>
-        <v>87.2668041237113</v>
+        <v>0.0618556701030928</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="7" t="n">
+      <c r="B18" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="8" t="n">
         <v>28006.15</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="H18" s="8" t="n">
         <v>10476.2</v>
       </c>
-      <c r="H18" s="6" t="n">
-        <f aca="false">IF(D18&gt;0,G18/D18,"")</f>
+      <c r="I18" s="7" t="n">
+        <f aca="false">IF(D18&gt;0,H18/D18,"")</f>
         <v>0.374067838671149</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="J18" s="3" t="n">
         <f aca="false">IF(AND(D18&gt;0,F18&gt;0),D18/F18,"")</f>
         <v>181.858116883117</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="K18" s="3" t="n">
+        <f aca="false">IF(AND(D18&gt;0,G18&gt;0),D18/G18,"")</f>
+        <v>683.076829268293</v>
+      </c>
+      <c r="L18" s="13" t="n">
         <f aca="false">IF(F18&gt;0,G18/F18,"")</f>
-        <v>68.0272727272727</v>
+        <v>0.266233766233766</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="7" t="n">
+      <c r="B19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>12078.04</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>10048</v>
       </c>
-      <c r="H19" s="6" t="n">
-        <f aca="false">IF(D19&gt;0,G19/D19,"")</f>
+      <c r="I19" s="7" t="n">
+        <f aca="false">IF(D19&gt;0,H19/D19,"")</f>
         <v>0.831923060364099</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="J19" s="3" t="n">
         <f aca="false">IF(AND(D19&gt;0,F19&gt;0),D19/F19,"")</f>
         <v>335.501111111111</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="K19" s="3" t="n">
+        <f aca="false">IF(AND(D19&gt;0,G19&gt;0),D19/G19,"")</f>
+        <v>1509.755</v>
+      </c>
+      <c r="L19" s="13" t="n">
         <f aca="false">IF(F19&gt;0,G19/F19,"")</f>
-        <v>279.111111111111</v>
+        <v>0.222222222222222</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="7" t="n">
+      <c r="B20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="8" t="n">
         <v>25375.44</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="8" t="n">
         <v>8126.51</v>
       </c>
-      <c r="H20" s="6" t="n">
-        <f aca="false">IF(D20&gt;0,G20/D20,"")</f>
+      <c r="I20" s="7" t="n">
+        <f aca="false">IF(D20&gt;0,H20/D20,"")</f>
         <v>0.320250998603374</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="J20" s="3" t="n">
         <f aca="false">IF(AND(D20&gt;0,F20&gt;0),D20/F20,"")</f>
         <v>342.911351351351</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="K20" s="3" t="n">
+        <f aca="false">IF(AND(D20&gt;0,G20&gt;0),D20/G20,"")</f>
+        <v>1268.772</v>
+      </c>
+      <c r="L20" s="13" t="n">
         <f aca="false">IF(F20&gt;0,G20/F20,"")</f>
-        <v>109.817702702703</v>
+        <v>0.27027027027027</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="11" t="n">
+      <c r="B21" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="8" t="n">
         <v>7469.08</v>
       </c>
-      <c r="H21" s="6" t="str">
-        <f aca="false">IF(D21&gt;0,G21/D21,"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="3" t="str">
+      <c r="I21" s="7" t="str">
+        <f aca="false">IF(D21&gt;0,H21/D21,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="3" t="str">
         <f aca="false">IF(AND(D21&gt;0,F21&gt;0),D21/F21,"")</f>
         <v/>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="K21" s="3" t="str">
+        <f aca="false">IF(AND(D21&gt;0,G21&gt;0),D21/G21,"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="13" t="n">
         <f aca="false">IF(F21&gt;0,G21/F21,"")</f>
-        <v>533.505714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="7" t="n">
+      <c r="B22" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>8099.74</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="8" t="n">
         <v>4832.62</v>
       </c>
-      <c r="H22" s="6" t="n">
-        <f aca="false">IF(D22&gt;0,G22/D22,"")</f>
+      <c r="I22" s="7" t="n">
+        <f aca="false">IF(D22&gt;0,H22/D22,"")</f>
         <v>0.596638904458662</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="J22" s="3" t="n">
         <f aca="false">IF(AND(D22&gt;0,F22&gt;0),D22/F22,"")</f>
         <v>130.640967741935</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="K22" s="3" t="n">
+        <f aca="false">IF(AND(D22&gt;0,G22&gt;0),D22/G22,"")</f>
+        <v>539.982666666667</v>
+      </c>
+      <c r="L22" s="13" t="n">
         <f aca="false">IF(F22&gt;0,G22/F22,"")</f>
-        <v>77.9454838709677</v>
+        <v>0.241935483870968</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>3671.52</v>
+      </c>
+      <c r="I23" s="7" t="str">
+        <f aca="false">IF(D23&gt;0,H23/D23,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="3" t="str">
+        <f aca="false">IF(AND(D23&gt;0,F23&gt;0),D23/F23,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="3" t="str">
+        <f aca="false">IF(AND(D23&gt;0,G23&gt;0),D23/G23,"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="13" t="n">
+        <f aca="false">IF(F23&gt;0,G23/F23,"")</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="11" t="n">
+      <c r="D24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>2781.41</v>
+      </c>
+      <c r="I24" s="7" t="str">
+        <f aca="false">IF(D24&gt;0,H24/D24,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="3" t="str">
+        <f aca="false">IF(AND(D24&gt;0,F24&gt;0),D24/F24,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="3" t="str">
+        <f aca="false">IF(AND(D24&gt;0,G24&gt;0),D24/G24,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="13" t="n">
+        <f aca="false">IF(F24&gt;0,G24/F24,"")</f>
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>2596.61</v>
+      </c>
+      <c r="I25" s="7" t="str">
+        <f aca="false">IF(D25&gt;0,H25/D25,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="3" t="str">
+        <f aca="false">IF(AND(D25&gt;0,F25&gt;0),D25/F25,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="3" t="str">
+        <f aca="false">IF(AND(D25&gt;0,G25&gt;0),D25/G25,"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="13" t="n">
+        <f aca="false">IF(F25&gt;0,G25/F25,"")</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>2237.4</v>
+      </c>
+      <c r="I26" s="7" t="str">
+        <f aca="false">IF(D26&gt;0,H26/D26,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f aca="false">IF(AND(D26&gt;0,F26&gt;0),D26/F26,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="3" t="str">
+        <f aca="false">IF(AND(D26&gt;0,G26&gt;0),D26/G26,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="13" t="n">
+        <f aca="false">IF(F26&gt;0,G26/F26,"")</f>
+        <v>0.37037037037037</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>1871.16</v>
+      </c>
+      <c r="I27" s="7" t="str">
+        <f aca="false">IF(D27&gt;0,H27/D27,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="3" t="str">
+        <f aca="false">IF(AND(D27&gt;0,F27&gt;0),D27/F27,"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="3" t="str">
+        <f aca="false">IF(AND(D27&gt;0,G27&gt;0),D27/G27,"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="13" t="n">
+        <f aca="false">IF(F27&gt;0,G27/F27,"")</f>
+        <v>0.0909090909090909</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>1814</v>
+      </c>
+      <c r="I28" s="7" t="str">
+        <f aca="false">IF(D28&gt;0,H28/D28,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="3" t="str">
+        <f aca="false">IF(AND(D28&gt;0,F28&gt;0),D28/F28,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="3" t="str">
+        <f aca="false">IF(AND(D28&gt;0,G28&gt;0),D28/G28,"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="13" t="n">
+        <f aca="false">IF(F28&gt;0,G28/F28,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1447.57</v>
+      </c>
+      <c r="I29" s="7" t="str">
+        <f aca="false">IF(D29&gt;0,H29/D29,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="3" t="str">
+        <f aca="false">IF(AND(D29&gt;0,F29&gt;0),D29/F29,"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="3" t="str">
+        <f aca="false">IF(AND(D29&gt;0,G29&gt;0),D29/G29,"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="13" t="n">
+        <f aca="false">IF(F29&gt;0,G29/F29,"")</f>
+        <v>0.380952380952381</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>1306.6</v>
+      </c>
+      <c r="I30" s="7" t="str">
+        <f aca="false">IF(D30&gt;0,H30/D30,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="3" t="str">
+        <f aca="false">IF(AND(D30&gt;0,F30&gt;0),D30/F30,"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="3" t="str">
+        <f aca="false">IF(AND(D30&gt;0,G30&gt;0),D30/G30,"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="13" t="n">
+        <f aca="false">IF(F30&gt;0,G30/F30,"")</f>
+        <v>0.170212765957447</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>1177.06</v>
+      </c>
+      <c r="I31" s="7" t="str">
+        <f aca="false">IF(D31&gt;0,H31/D31,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="3" t="str">
+        <f aca="false">IF(AND(D31&gt;0,F31&gt;0),D31/F31,"")</f>
+        <v/>
+      </c>
+      <c r="K31" s="3" t="str">
+        <f aca="false">IF(AND(D31&gt;0,G31&gt;0),D31/G31,"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="13" t="n">
+        <f aca="false">IF(F31&gt;0,G31/F31,"")</f>
+        <v>0.555555555555556</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>1173.92</v>
+      </c>
+      <c r="I32" s="7" t="str">
+        <f aca="false">IF(D32&gt;0,H32/D32,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="3" t="str">
+        <f aca="false">IF(AND(D32&gt;0,F32&gt;0),D32/F32,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="3" t="str">
+        <f aca="false">IF(AND(D32&gt;0,G32&gt;0),D32/G32,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="13" t="n">
+        <f aca="false">IF(F32&gt;0,G32/F32,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>3671.52</v>
-      </c>
-      <c r="H23" s="6" t="str">
-        <f aca="false">IF(D23&gt;0,G23/D23,"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="3" t="str">
-        <f aca="false">IF(AND(D23&gt;0,F23&gt;0),D23/F23,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="3" t="n">
-        <f aca="false">IF(F23&gt;0,G23/F23,"")</f>
-        <v>305.96</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>2781.41</v>
-      </c>
-      <c r="H24" s="6" t="str">
-        <f aca="false">IF(D24&gt;0,G24/D24,"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="3" t="str">
-        <f aca="false">IF(AND(D24&gt;0,F24&gt;0),D24/F24,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="3" t="n">
-        <f aca="false">IF(F24&gt;0,G24/F24,"")</f>
-        <v>115.892083333333</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>2596.61</v>
-      </c>
-      <c r="H25" s="6" t="str">
-        <f aca="false">IF(D25&gt;0,G25/D25,"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="3" t="str">
-        <f aca="false">IF(AND(D25&gt;0,F25&gt;0),D25/F25,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="3" t="n">
-        <f aca="false">IF(F25&gt;0,G25/F25,"")</f>
-        <v>103.8644</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>2237.4</v>
-      </c>
-      <c r="H26" s="6" t="str">
-        <f aca="false">IF(D26&gt;0,G26/D26,"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="3" t="str">
-        <f aca="false">IF(AND(D26&gt;0,F26&gt;0),D26/F26,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="3" t="n">
-        <f aca="false">IF(F26&gt;0,G26/F26,"")</f>
-        <v>82.8666666666667</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>1871.16</v>
-      </c>
-      <c r="H27" s="6" t="str">
-        <f aca="false">IF(D27&gt;0,G27/D27,"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="3" t="str">
-        <f aca="false">IF(AND(D27&gt;0,F27&gt;0),D27/F27,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="3" t="n">
-        <f aca="false">IF(F27&gt;0,G27/F27,"")</f>
-        <v>170.105454545455</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>1814</v>
-      </c>
-      <c r="H28" s="6" t="str">
-        <f aca="false">IF(D28&gt;0,G28/D28,"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="3" t="str">
-        <f aca="false">IF(AND(D28&gt;0,F28&gt;0),D28/F28,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="3" t="n">
-        <f aca="false">IF(F28&gt;0,G28/F28,"")</f>
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>1447.57</v>
-      </c>
-      <c r="H29" s="6" t="str">
-        <f aca="false">IF(D29&gt;0,G29/D29,"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="3" t="str">
-        <f aca="false">IF(AND(D29&gt;0,F29&gt;0),D29/F29,"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="3" t="n">
-        <f aca="false">IF(F29&gt;0,G29/F29,"")</f>
-        <v>68.9319047619048</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>67</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>1306.6</v>
-      </c>
-      <c r="H30" s="6" t="str">
-        <f aca="false">IF(D30&gt;0,G30/D30,"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="3" t="str">
-        <f aca="false">IF(AND(D30&gt;0,F30&gt;0),D30/F30,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="3" t="n">
-        <f aca="false">IF(F30&gt;0,G30/F30,"")</f>
-        <v>27.8</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>1177.06</v>
-      </c>
-      <c r="H31" s="6" t="str">
-        <f aca="false">IF(D31&gt;0,G31/D31,"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="3" t="str">
-        <f aca="false">IF(AND(D31&gt;0,F31&gt;0),D31/F31,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="3" t="n">
-        <f aca="false">IF(F31&gt;0,G31/F31,"")</f>
-        <v>130.784444444444</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>1173.92</v>
-      </c>
-      <c r="H32" s="6" t="str">
-        <f aca="false">IF(D32&gt;0,G32/D32,"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="3" t="str">
-        <f aca="false">IF(AND(D32&gt;0,F32&gt;0),D32/F32,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="3" t="n">
-        <f aca="false">IF(F32&gt;0,G32/F32,"")</f>
-        <v>586.96</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="7" t="n">
+      <c r="C33" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="8" t="n">
         <v>3662.97</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="8" t="n">
         <v>1145.68</v>
       </c>
-      <c r="H33" s="6" t="n">
-        <f aca="false">IF(D33&gt;0,G33/D33,"")</f>
+      <c r="I33" s="7" t="n">
+        <f aca="false">IF(D33&gt;0,H33/D33,"")</f>
         <v>0.312773514388597</v>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="J33" s="3" t="n">
         <f aca="false">IF(AND(D33&gt;0,F33&gt;0),D33/F33,"")</f>
         <v>66.5994545454546</v>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="K33" s="3" t="n">
+        <f aca="false">IF(AND(D33&gt;0,G33&gt;0),D33/G33,"")</f>
+        <v>915.7425</v>
+      </c>
+      <c r="L33" s="13" t="n">
         <f aca="false">IF(F33&gt;0,G33/F33,"")</f>
-        <v>20.8305454545455</v>
+        <v>0.0727272727272727</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="11" t="n">
+      <c r="B34" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="8" t="n">
         <v>450</v>
       </c>
-      <c r="H34" s="6" t="str">
-        <f aca="false">IF(D34&gt;0,G34/D34,"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="3" t="str">
+      <c r="I34" s="7" t="str">
+        <f aca="false">IF(D34&gt;0,H34/D34,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="3" t="str">
         <f aca="false">IF(AND(D34&gt;0,F34&gt;0),D34/F34,"")</f>
         <v/>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="K34" s="3" t="str">
+        <f aca="false">IF(AND(D34&gt;0,G34&gt;0),D34/G34,"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="13" t="n">
         <f aca="false">IF(F34&gt;0,G34/F34,"")</f>
-        <v>450</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="11" t="n">
+      <c r="B35" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" s="8" t="n">
         <v>403.91</v>
       </c>
-      <c r="H35" s="6" t="str">
-        <f aca="false">IF(D35&gt;0,G35/D35,"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="3" t="str">
+      <c r="I35" s="7" t="str">
+        <f aca="false">IF(D35&gt;0,H35/D35,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="3" t="str">
         <f aca="false">IF(AND(D35&gt;0,F35&gt;0),D35/F35,"")</f>
         <v/>
       </c>
-      <c r="J35" s="3" t="n">
+      <c r="K35" s="3" t="str">
+        <f aca="false">IF(AND(D35&gt;0,G35&gt;0),D35/G35,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="13" t="n">
         <f aca="false">IF(F35&gt;0,G35/F35,"")</f>
-        <v>28.8507142857143</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="11" t="n">
+      <c r="B36" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="8" t="n">
         <v>374.6</v>
       </c>
-      <c r="H36" s="6" t="str">
-        <f aca="false">IF(D36&gt;0,G36/D36,"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="3" t="str">
+      <c r="I36" s="7" t="str">
+        <f aca="false">IF(D36&gt;0,H36/D36,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="3" t="str">
         <f aca="false">IF(AND(D36&gt;0,F36&gt;0),D36/F36,"")</f>
         <v/>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="K36" s="3" t="str">
+        <f aca="false">IF(AND(D36&gt;0,G36&gt;0),D36/G36,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="13" t="n">
         <f aca="false">IF(F36&gt;0,G36/F36,"")</f>
-        <v>37.46</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="7" t="n">
+      <c r="B37" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="8" t="n">
         <v>2313.2</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="8" t="n">
         <v>319</v>
       </c>
-      <c r="H37" s="6" t="n">
-        <f aca="false">IF(D37&gt;0,G37/D37,"")</f>
+      <c r="I37" s="7" t="n">
+        <f aca="false">IF(D37&gt;0,H37/D37,"")</f>
         <v>0.137904201971295</v>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="J37" s="3" t="n">
         <f aca="false">IF(AND(D37&gt;0,F37&gt;0),D37/F37,"")</f>
         <v>330.457142857143</v>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="K37" s="3" t="n">
+        <f aca="false">IF(AND(D37&gt;0,G37&gt;0),D37/G37,"")</f>
+        <v>2313.2</v>
+      </c>
+      <c r="L37" s="13" t="n">
         <f aca="false">IF(F37&gt;0,G37/F37,"")</f>
-        <v>45.5714285714286</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="n">
+      <c r="A38" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="8" t="s">
+      <c r="B38" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="I38" s="7" t="str">
+        <f aca="false">IF(D38&gt;0,H38/D38,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="3" t="str">
+        <f aca="false">IF(AND(D38&gt;0,F38&gt;0),D38/F38,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="3" t="str">
+        <f aca="false">IF(AND(D38&gt;0,G38&gt;0),D38/G38,"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="13" t="n">
+        <f aca="false">IF(F38&gt;0,G38/F38,"")</f>
+        <v>0.111111111111111</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7" t="str">
+        <f aca="false">IF(D39&gt;0,H39/D39,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="3" t="str">
+        <f aca="false">IF(AND(D39&gt;0,F39&gt;0),D39/F39,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="3" t="str">
+        <f aca="false">IF(AND(D39&gt;0,G39&gt;0),D39/G39,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="13" t="n">
+        <f aca="false">IF(F39&gt;0,G39/F39,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>5022.32</v>
+      </c>
+      <c r="E40" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="H38" s="6" t="str">
-        <f aca="false">IF(D38&gt;0,G38/D38,"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="3" t="str">
-        <f aca="false">IF(AND(D38&gt;0,F38&gt;0),D38/F38,"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="3" t="n">
-        <f aca="false">IF(F38&gt;0,G38/F38,"")</f>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>173</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>151</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="6" t="str">
-        <f aca="false">IF(D39&gt;0,G39/D39,"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="3" t="str">
-        <f aca="false">IF(AND(D39&gt;0,F39&gt;0),D39/F39,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="3" t="n">
-        <f aca="false">IF(F39&gt;0,G39/F39,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>5022.32</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="G40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <f aca="false">IF(D40&gt;0,G40/D40,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="3" t="n">
+      <c r="G40" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <f aca="false">IF(D40&gt;0,H40/D40,"")</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="n">
         <f aca="false">IF(AND(D40&gt;0,F40&gt;0),D40/F40,"")</f>
         <v>218.361739130435</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="K40" s="3" t="n">
+        <f aca="false">IF(AND(D40&gt;0,G40&gt;0),D40/G40,"")</f>
+        <v>2511.16</v>
+      </c>
+      <c r="L40" s="13" t="n">
         <f aca="false">IF(F40&gt;0,G40/F40,"")</f>
-        <v>0</v>
+        <v>0.0869565217391304</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="11" t="n">
+      <c r="B41" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="6" t="str">
-        <f aca="false">IF(D41&gt;0,G41/D41,"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="3" t="str">
+      <c r="G41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="7" t="str">
+        <f aca="false">IF(D41&gt;0,H41/D41,"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="3" t="str">
         <f aca="false">IF(AND(D41&gt;0,F41&gt;0),D41/F41,"")</f>
         <v/>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="K41" s="3" t="str">
+        <f aca="false">IF(AND(D41&gt;0,G41&gt;0),D41/G41,"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="13" t="n">
         <f aca="false">IF(F41&gt;0,G41/F41,"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="11" t="n">
+      <c r="B42" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="6" t="str">
-        <f aca="false">IF(D42&gt;0,G42/D42,"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="3" t="str">
+      <c r="G42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7" t="str">
+        <f aca="false">IF(D42&gt;0,H42/D42,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="3" t="str">
         <f aca="false">IF(AND(D42&gt;0,F42&gt;0),D42/F42,"")</f>
         <v/>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="K42" s="3" t="str">
+        <f aca="false">IF(AND(D42&gt;0,G42&gt;0),D42/G42,"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="13" t="n">
         <f aca="false">IF(F42&gt;0,G42/F42,"")</f>
-        <v>0</v>
+        <v>0.444444444444444</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="n">
+      <c r="A43" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="11" t="n">
+      <c r="B43" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="str">
-        <f aca="false">IF(D43&gt;0,G43/D43,"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="3" t="str">
+      <c r="G43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7" t="str">
+        <f aca="false">IF(D43&gt;0,H43/D43,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="3" t="str">
         <f aca="false">IF(AND(D43&gt;0,F43&gt;0),D43/F43,"")</f>
         <v/>
       </c>
-      <c r="J43" s="3" t="n">
+      <c r="K43" s="3" t="str">
+        <f aca="false">IF(AND(D43&gt;0,G43&gt;0),D43/G43,"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="13" t="n">
         <f aca="false">IF(F43&gt;0,G43/F43,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="n">
+      <c r="A44" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="7" t="n">
+      <c r="B44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="8" t="n">
         <v>2081.75</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <f aca="false">IF(D44&gt;0,G44/D44,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="n">
+      <c r="G44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <f aca="false">IF(D44&gt;0,H44/D44,"")</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <f aca="false">IF(AND(D44&gt;0,F44&gt;0),D44/F44,"")</f>
         <v>416.35</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="K44" s="3" t="str">
+        <f aca="false">IF(AND(D44&gt;0,G44&gt;0),D44/G44,"")</f>
+        <v/>
+      </c>
+      <c r="L44" s="13" t="n">
         <f aca="false">IF(F44&gt;0,G44/F44,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="n">
+      <c r="A45" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="7" t="n">
+      <c r="B45" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>828.25</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F45" s="11" t="n">
+      <c r="F45" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <f aca="false">IF(D45&gt;0,G45/D45,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="n">
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <f aca="false">IF(D45&gt;0,H45/D45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="n">
         <f aca="false">IF(AND(D45&gt;0,F45&gt;0),D45/F45,"")</f>
         <v>165.65</v>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="K45" s="3" t="str">
+        <f aca="false">IF(AND(D45&gt;0,G45&gt;0),D45/G45,"")</f>
+        <v/>
+      </c>
+      <c r="L45" s="13" t="n">
         <f aca="false">IF(F45&gt;0,G45/F45,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="n">
+      <c r="A46" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="11" t="n">
+      <c r="B46" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="6" t="str">
-        <f aca="false">IF(D46&gt;0,G46/D46,"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="3" t="str">
+      <c r="G46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7" t="str">
+        <f aca="false">IF(D46&gt;0,H46/D46,"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="3" t="str">
         <f aca="false">IF(AND(D46&gt;0,F46&gt;0),D46/F46,"")</f>
         <v/>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="K46" s="3" t="str">
+        <f aca="false">IF(AND(D46&gt;0,G46&gt;0),D46/G46,"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="13" t="n">
         <f aca="false">IF(F46&gt;0,G46/F46,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="n">
+      <c r="A47" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="11" t="n">
+      <c r="B47" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="F47" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="6" t="str">
-        <f aca="false">IF(D47&gt;0,G47/D47,"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="3" t="str">
+      <c r="G47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7" t="str">
+        <f aca="false">IF(D47&gt;0,H47/D47,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="3" t="str">
         <f aca="false">IF(AND(D47&gt;0,F47&gt;0),D47/F47,"")</f>
         <v/>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="K47" s="3" t="str">
+        <f aca="false">IF(AND(D47&gt;0,G47&gt;0),D47/G47,"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="13" t="n">
         <f aca="false">IF(F47&gt;0,G47/F47,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="n">
+      <c r="A48" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="11" t="n">
+      <c r="B48" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F48" s="11" t="n">
+      <c r="F48" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="6" t="str">
-        <f aca="false">IF(D48&gt;0,G48/D48,"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="3" t="str">
+      <c r="G48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7" t="str">
+        <f aca="false">IF(D48&gt;0,H48/D48,"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="3" t="str">
         <f aca="false">IF(AND(D48&gt;0,F48&gt;0),D48/F48,"")</f>
         <v/>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="K48" s="3" t="str">
+        <f aca="false">IF(AND(D48&gt;0,G48&gt;0),D48/G48,"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="13" t="n">
         <f aca="false">IF(F48&gt;0,G48/F48,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="n">
+      <c r="A49" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="11" t="n">
+      <c r="B49" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="11" t="n">
+      <c r="F49" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="6" t="str">
-        <f aca="false">IF(D49&gt;0,G49/D49,"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="3" t="str">
+      <c r="G49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7" t="str">
+        <f aca="false">IF(D49&gt;0,H49/D49,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="3" t="str">
         <f aca="false">IF(AND(D49&gt;0,F49&gt;0),D49/F49,"")</f>
         <v/>
       </c>
-      <c r="J49" s="3" t="n">
+      <c r="K49" s="3" t="str">
+        <f aca="false">IF(AND(D49&gt;0,G49&gt;0),D49/G49,"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="13" t="n">
         <f aca="false">IF(F49&gt;0,G49/F49,"")</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="n">
+      <c r="A50" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="8" t="s">
+      <c r="B50" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7" t="str">
+        <f aca="false">IF(D50&gt;0,H50/D50,"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="3" t="str">
+        <f aca="false">IF(AND(D50&gt;0,F50&gt;0),D50/F50,"")</f>
+        <v/>
+      </c>
+      <c r="K50" s="3" t="str">
+        <f aca="false">IF(AND(D50&gt;0,G50&gt;0),D50/G50,"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="13" t="n">
+        <f aca="false">IF(F50&gt;0,G50/F50,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="11" t="n">
+      <c r="D51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="7" t="str">
+        <f aca="false">IF(D51&gt;0,H51/D51,"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="3" t="str">
+        <f aca="false">IF(AND(D51&gt;0,F51&gt;0),D51/F51,"")</f>
+        <v/>
+      </c>
+      <c r="K51" s="3" t="str">
+        <f aca="false">IF(AND(D51&gt;0,G51&gt;0),D51/G51,"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="13" t="n">
+        <f aca="false">IF(F51&gt;0,G51/F51,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F50" s="11" t="n">
+      <c r="F52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="6" t="str">
-        <f aca="false">IF(D50&gt;0,G50/D50,"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="3" t="str">
-        <f aca="false">IF(AND(D50&gt;0,F50&gt;0),D50/F50,"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="3" t="n">
-        <f aca="false">IF(F50&gt;0,G50/F50,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="11" t="n">
+      <c r="G52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7" t="str">
+        <f aca="false">IF(D52&gt;0,H52/D52,"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="3" t="str">
+        <f aca="false">IF(AND(D52&gt;0,F52&gt;0),D52/F52,"")</f>
+        <v/>
+      </c>
+      <c r="K52" s="3" t="str">
+        <f aca="false">IF(AND(D52&gt;0,G52&gt;0),D52/G52,"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="13" t="n">
+        <f aca="false">IF(F52&gt;0,G52/F52,"")</f>
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F51" s="11" t="n">
+      <c r="G53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="7" t="str">
+        <f aca="false">IF(D53&gt;0,H53/D53,"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="3" t="str">
+        <f aca="false">IF(AND(D53&gt;0,F53&gt;0),D53/F53,"")</f>
+        <v/>
+      </c>
+      <c r="K53" s="3" t="str">
+        <f aca="false">IF(AND(D53&gt;0,G53&gt;0),D53/G53,"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="13" t="n">
+        <f aca="false">IF(F53&gt;0,G53/F53,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="6" t="str">
-        <f aca="false">IF(D51&gt;0,G51/D51,"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="3" t="str">
-        <f aca="false">IF(AND(D51&gt;0,F51&gt;0),D51/F51,"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="3" t="n">
-        <f aca="false">IF(F51&gt;0,G51/F51,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F52" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="6" t="str">
-        <f aca="false">IF(D52&gt;0,G52/D52,"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="3" t="str">
-        <f aca="false">IF(AND(D52&gt;0,F52&gt;0),D52/F52,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="3" t="n">
-        <f aca="false">IF(F52&gt;0,G52/F52,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="6" t="str">
-        <f aca="false">IF(D53&gt;0,G53/D53,"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="3" t="str">
-        <f aca="false">IF(AND(D53&gt;0,F53&gt;0),D53/F53,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="3" t="n">
-        <f aca="false">IF(F53&gt;0,G53/F53,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" s="11" t="n">
+      <c r="F54" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="str">
-        <f aca="false">IF(D54&gt;0,G54/D54,"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="3" t="str">
+      <c r="G54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="7" t="str">
+        <f aca="false">IF(D54&gt;0,H54/D54,"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="3" t="str">
         <f aca="false">IF(AND(D54&gt;0,F54&gt;0),D54/F54,"")</f>
         <v/>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="K54" s="3" t="str">
+        <f aca="false">IF(AND(D54&gt;0,G54&gt;0),D54/G54,"")</f>
+        <v/>
+      </c>
+      <c r="L54" s="13" t="n">
         <f aca="false">IF(F54&gt;0,G54/F54,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="n">
+      <c r="A55" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="11" t="n">
+      <c r="B55" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="11" t="n">
+      <c r="F55" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="6" t="str">
-        <f aca="false">IF(D55&gt;0,G55/D55,"")</f>
-        <v/>
-      </c>
-      <c r="I55" s="3" t="str">
+      <c r="G55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="7" t="str">
+        <f aca="false">IF(D55&gt;0,H55/D55,"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="3" t="str">
         <f aca="false">IF(AND(D55&gt;0,F55&gt;0),D55/F55,"")</f>
         <v/>
       </c>
-      <c r="J55" s="3" t="n">
+      <c r="K55" s="3" t="str">
+        <f aca="false">IF(AND(D55&gt;0,G55&gt;0),D55/G55,"")</f>
+        <v/>
+      </c>
+      <c r="L55" s="13" t="n">
         <f aca="false">IF(F55&gt;0,G55/F55,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="n">
+      <c r="A56" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D56" s="7" t="n">
+      <c r="B56" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" s="8" t="n">
         <v>344.89</v>
       </c>
-      <c r="E56" s="11" t="n">
+      <c r="E56" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="11" t="n">
+      <c r="F56" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <f aca="false">IF(D56&gt;0,G56/D56,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="3" t="n">
+      <c r="G56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <f aca="false">IF(D56&gt;0,H56/D56,"")</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="n">
         <f aca="false">IF(AND(D56&gt;0,F56&gt;0),D56/F56,"")</f>
         <v>344.89</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="K56" s="3" t="str">
+        <f aca="false">IF(AND(D56&gt;0,G56&gt;0),D56/G56,"")</f>
+        <v/>
+      </c>
+      <c r="L56" s="13" t="n">
         <f aca="false">IF(F56&gt;0,G56/F56,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="n">
+      <c r="A57" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="8" t="s">
+      <c r="B57" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="7" t="str">
+        <f aca="false">IF(D57&gt;0,H57/D57,"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="3" t="str">
+        <f aca="false">IF(AND(D57&gt;0,F57&gt;0),D57/F57,"")</f>
+        <v/>
+      </c>
+      <c r="K57" s="3" t="str">
+        <f aca="false">IF(AND(D57&gt;0,G57&gt;0),D57/G57,"")</f>
+        <v/>
+      </c>
+      <c r="L57" s="13" t="n">
+        <f aca="false">IF(F57&gt;0,G57/F57,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="7" t="str">
+        <f aca="false">IF(D58&gt;0,H58/D58,"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="3" t="str">
+        <f aca="false">IF(AND(D58&gt;0,F58&gt;0),D58/F58,"")</f>
+        <v/>
+      </c>
+      <c r="K58" s="3" t="str">
+        <f aca="false">IF(AND(D58&gt;0,G58&gt;0),D58/G58,"")</f>
+        <v/>
+      </c>
+      <c r="L58" s="13" t="n">
+        <f aca="false">IF(F58&gt;0,G58/F58,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="7" t="str">
+        <f aca="false">IF(D59&gt;0,H59/D59,"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="3" t="str">
+        <f aca="false">IF(AND(D59&gt;0,F59&gt;0),D59/F59,"")</f>
+        <v/>
+      </c>
+      <c r="K59" s="3" t="str">
+        <f aca="false">IF(AND(D59&gt;0,G59&gt;0),D59/G59,"")</f>
+        <v/>
+      </c>
+      <c r="L59" s="13" t="n">
+        <f aca="false">IF(F59&gt;0,G59/F59,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="11" t="n">
+      <c r="D60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="6" t="str">
-        <f aca="false">IF(D57&gt;0,G57/D57,"")</f>
-        <v/>
-      </c>
-      <c r="I57" s="3" t="str">
-        <f aca="false">IF(AND(D57&gt;0,F57&gt;0),D57/F57,"")</f>
-        <v/>
-      </c>
-      <c r="J57" s="3" t="n">
-        <f aca="false">IF(F57&gt;0,G57/F57,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="str">
-        <f aca="false">IF(D58&gt;0,G58/D58,"")</f>
-        <v/>
-      </c>
-      <c r="I58" s="3" t="str">
-        <f aca="false">IF(AND(D58&gt;0,F58&gt;0),D58/F58,"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="3" t="n">
-        <f aca="false">IF(F58&gt;0,G58/F58,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F59" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="6" t="str">
-        <f aca="false">IF(D59&gt;0,G59/D59,"")</f>
-        <v/>
-      </c>
-      <c r="I59" s="3" t="str">
-        <f aca="false">IF(AND(D59&gt;0,F59&gt;0),D59/F59,"")</f>
-        <v/>
-      </c>
-      <c r="J59" s="3" t="n">
-        <f aca="false">IF(F59&gt;0,G59/F59,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="6" t="str">
-        <f aca="false">IF(D60&gt;0,G60/D60,"")</f>
-        <v/>
-      </c>
-      <c r="I60" s="3" t="str">
+      <c r="F60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="7" t="str">
+        <f aca="false">IF(D60&gt;0,H60/D60,"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="3" t="str">
         <f aca="false">IF(AND(D60&gt;0,F60&gt;0),D60/F60,"")</f>
         <v/>
       </c>
-      <c r="J60" s="3" t="str">
+      <c r="K60" s="3" t="str">
+        <f aca="false">IF(AND(D60&gt;0,G60&gt;0),D60/G60,"")</f>
+        <v/>
+      </c>
+      <c r="L60" s="13" t="str">
         <f aca="false">IF(F60&gt;0,G60/F60,"")</f>
         <v/>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="7" t="n">
+      <c r="B61" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" s="8" t="n">
         <v>5064.61</v>
       </c>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D62" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="D62" s="18" t="n">
         <f aca="false">SUM(D5:D61)</f>
         <v>173871.59</v>
       </c>
-      <c r="E62" s="16" t="n">
+      <c r="E62" s="19" t="n">
         <f aca="false">SUM(E5:E61)</f>
         <v>5007</v>
       </c>
-      <c r="F62" s="16" t="n">
+      <c r="F62" s="19" t="n">
         <f aca="false">SUM(F5:F61)</f>
         <v>3613</v>
       </c>
-      <c r="G62" s="15" t="n">
+      <c r="G62" s="19" t="n">
         <f aca="false">SUM(G5:G61)</f>
+        <v>714</v>
+      </c>
+      <c r="H62" s="18" t="n">
+        <f aca="false">SUM(H5:H61)</f>
         <v>841452.23</v>
       </c>
-      <c r="H62" s="17" t="n">
-        <f aca="false">G62/D62</f>
+      <c r="I62" s="20" t="n">
+        <f aca="false">H62/D62</f>
         <v>4.83950385454001</v>
       </c>
-      <c r="I62" s="15" t="n">
+      <c r="J62" s="18" t="n">
         <f aca="false">D62/F62</f>
         <v>48.1238831995572</v>
       </c>
-      <c r="J62" s="15" t="n">
+      <c r="K62" s="18" t="n">
+        <f aca="false">D62/G62</f>
+        <v>243.517633053221</v>
+      </c>
+      <c r="L62" s="21" t="n">
         <f aca="false">G62/F62</f>
-        <v>232.89571823969</v>
+        <v>0.197619706615001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J60"/>
+  <autoFilter ref="A4:L60"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3023,48 +3483,56 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="A3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>6</v>
+      <c r="E3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>24</v>
+      <c r="A4" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$D$5:$D$61,'All Campaigns Ranked'!$C$5:$C$61,$A4)</f>
@@ -3078,22 +3546,30 @@
         <f aca="false">SUMIFS('All Campaigns Ranked'!$F$5:$F$61,'All Campaigns Ranked'!$C$5:$C$61,$A4)</f>
         <v>1135</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$G$5:$G$61,'All Campaigns Ranked'!$C$5:$C$61,$A4)</f>
+        <v>155</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <f aca="false">SUMIFS('All Campaigns Ranked'!$H$5:$H$61,'All Campaigns Ranked'!$C$5:$C$61,$A4)</f>
         <v>351992.73</v>
       </c>
-      <c r="F4" s="18" t="n">
-        <f aca="false">E4/$E$10</f>
+      <c r="G4" s="22" t="n">
+        <f aca="false">F4/$F$10</f>
         <v>0.418315761074161</v>
       </c>
-      <c r="G4" s="6" t="str">
-        <f aca="false">IF(B4&gt;0,E4/B4,"")</f>
-        <v/>
+      <c r="H4" s="7" t="str">
+        <f aca="false">IF(B4&gt;0,F4/B4,"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="13" t="n">
+        <f aca="false">IF(D4&gt;0,E4/D4,"")</f>
+        <v>0.136563876651982</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>28</v>
+      <c r="A5" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$D$5:$D$61,'All Campaigns Ranked'!$C$5:$C$61,$A5)</f>
@@ -3107,22 +3583,30 @@
         <f aca="false">SUMIFS('All Campaigns Ranked'!$F$5:$F$61,'All Campaigns Ranked'!$C$5:$C$61,$A5)</f>
         <v>1820</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$G$5:$G$61,'All Campaigns Ranked'!$C$5:$C$61,$A5)</f>
+        <v>474</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <f aca="false">SUMIFS('All Campaigns Ranked'!$H$5:$H$61,'All Campaigns Ranked'!$C$5:$C$61,$A5)</f>
         <v>348694.48</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <f aca="false">E5/$E$10</f>
+      <c r="G5" s="22" t="n">
+        <f aca="false">F5/$F$10</f>
         <v>0.41439604955352</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <f aca="false">IF(B5&gt;0,E5/B5,"")</f>
+      <c r="H5" s="7" t="n">
+        <f aca="false">IF(B5&gt;0,F5/B5,"")</f>
         <v>2.00547127912041</v>
       </c>
+      <c r="I5" s="13" t="n">
+        <f aca="false">IF(D5&gt;0,E5/D5,"")</f>
+        <v>0.26043956043956</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>26</v>
+      <c r="A6" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$D$5:$D$61,'All Campaigns Ranked'!$C$5:$C$61,$A6)</f>
@@ -3136,22 +3620,30 @@
         <f aca="false">SUMIFS('All Campaigns Ranked'!$F$5:$F$61,'All Campaigns Ranked'!$C$5:$C$61,$A6)</f>
         <v>530</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$G$5:$G$61,'All Campaigns Ranked'!$C$5:$C$61,$A6)</f>
+        <v>64</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <f aca="false">SUMIFS('All Campaigns Ranked'!$H$5:$H$61,'All Campaigns Ranked'!$C$5:$C$61,$A6)</f>
         <v>122598.8</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <f aca="false">E6/$E$10</f>
+      <c r="G6" s="22" t="n">
+        <f aca="false">F6/$F$10</f>
         <v>0.145699061252711</v>
       </c>
-      <c r="G6" s="6" t="str">
-        <f aca="false">IF(B6&gt;0,E6/B6,"")</f>
-        <v/>
+      <c r="H6" s="7" t="str">
+        <f aca="false">IF(B6&gt;0,F6/B6,"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="13" t="n">
+        <f aca="false">IF(D6&gt;0,E6/D6,"")</f>
+        <v>0.120754716981132</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>38</v>
+      <c r="A7" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="B7" s="3" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$D$5:$D$61,'All Campaigns Ranked'!$C$5:$C$61,$A7)</f>
@@ -3165,22 +3657,30 @@
         <f aca="false">SUMIFS('All Campaigns Ranked'!$F$5:$F$61,'All Campaigns Ranked'!$C$5:$C$61,$A7)</f>
         <v>111</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$G$5:$G$61,'All Campaigns Ranked'!$C$5:$C$61,$A7)</f>
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <f aca="false">SUMIFS('All Campaigns Ranked'!$H$5:$H$61,'All Campaigns Ranked'!$C$5:$C$61,$A7)</f>
         <v>16989.16</v>
       </c>
-      <c r="F7" s="18" t="n">
-        <f aca="false">E7/$E$10</f>
+      <c r="G7" s="22" t="n">
+        <f aca="false">F7/$F$10</f>
         <v>0.020190284598806</v>
       </c>
-      <c r="G7" s="6" t="str">
-        <f aca="false">IF(B7&gt;0,E7/B7,"")</f>
-        <v/>
+      <c r="H7" s="7" t="str">
+        <f aca="false">IF(B7&gt;0,F7/B7,"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="13" t="n">
+        <f aca="false">IF(D7&gt;0,E7/D7,"")</f>
+        <v>0.126126126126126</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>52</v>
+      <c r="A8" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="B8" s="3" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$D$5:$D$61,'All Campaigns Ranked'!$C$5:$C$61,$A8)</f>
@@ -3194,22 +3694,30 @@
         <f aca="false">SUMIFS('All Campaigns Ranked'!$F$5:$F$61,'All Campaigns Ranked'!$C$5:$C$61,$A8)</f>
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$G$5:$G$61,'All Campaigns Ranked'!$C$5:$C$61,$A8)</f>
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <f aca="false">SUMIFS('All Campaigns Ranked'!$H$5:$H$61,'All Campaigns Ranked'!$C$5:$C$61,$A8)</f>
         <v>1177.06</v>
       </c>
-      <c r="F8" s="18" t="n">
-        <f aca="false">E8/$E$10</f>
+      <c r="G8" s="22" t="n">
+        <f aca="false">F8/$F$10</f>
         <v>0.00139884352080213</v>
       </c>
-      <c r="G8" s="6" t="str">
-        <f aca="false">IF(B8&gt;0,E8/B8,"")</f>
-        <v/>
+      <c r="H8" s="7" t="str">
+        <f aca="false">IF(B8&gt;0,F8/B8,"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="13" t="n">
+        <f aca="false">IF(D8&gt;0,E8/D8,"")</f>
+        <v>0.555555555555556</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>67</v>
+      <c r="A9" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="B9" s="3" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$D$5:$D$61,'All Campaigns Ranked'!$C$5:$C$61,$A9)</f>
@@ -3223,46 +3731,62 @@
         <f aca="false">SUMIFS('All Campaigns Ranked'!$F$5:$F$61,'All Campaigns Ranked'!$C$5:$C$61,$A9)</f>
         <v>8</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <f aca="false">SUMIFS('All Campaigns Ranked'!$G$5:$G$61,'All Campaigns Ranked'!$C$5:$C$61,$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <f aca="false">E9/$E$10</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="str">
-        <f aca="false">IF(B9&gt;0,E9/B9,"")</f>
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <f aca="false">SUMIFS('All Campaigns Ranked'!$H$5:$H$61,'All Campaigns Ranked'!$C$5:$C$61,$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <f aca="false">F9/$F$10</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f aca="false">IF(B9&gt;0,F9/B9,"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="13" t="n">
+        <f aca="false">IF(D9&gt;0,E9/D9,"")</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="B10" s="18" t="n">
         <f aca="false">SUM(B4:B9)</f>
         <v>173871.59</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="19" t="n">
         <f aca="false">SUM(C4:C9)</f>
         <v>5007</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="19" t="n">
         <f aca="false">SUM(D4:D9)</f>
         <v>3613</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="19" t="n">
         <f aca="false">SUM(E4:E9)</f>
+        <v>714</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <f aca="false">SUM(F4:F9)</f>
         <v>841452.23</v>
       </c>
-      <c r="F10" s="19" t="n">
-        <f aca="false">SUM(F4:F9)</f>
+      <c r="G10" s="23" t="n">
+        <f aca="false">SUM(G4:G9)</f>
         <v>1</v>
       </c>
-      <c r="G10" s="17" t="n">
-        <f aca="false">E10/B10</f>
+      <c r="H10" s="20" t="n">
+        <f aca="false">F10/B10</f>
         <v>4.83950385454001</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <f aca="false">E10/D10</f>
+        <v>0.197619706615001</v>
       </c>
     </row>
   </sheetData>
